--- a/sindicatosistema.xlsx
+++ b/sindicatosistema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Script\mediadorcct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DA87FE-9C20-4731-80A4-9AB46F30F9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC06A828-D69E-47B3-855F-8ED66A3C4AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CABB84FB-89BB-461F-AA55-12C3EDF7DC4B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CABB84FB-89BB-461F-AA55-12C3EDF7DC4B}"/>
   </bookViews>
   <sheets>
     <sheet name="cnpjs" sheetId="1" r:id="rId1"/>
@@ -47,9 +47,6 @@
     <t>SINDICATO DOS TRABALHADORES NAS INDUSTRIAS DA FIACAO, TECELAGEM E VESTUARIO DE CHAPECO E OESTE DE SANTA CATARINA</t>
   </si>
   <si>
-    <t>sindicato</t>
-  </si>
-  <si>
     <t>SIND TRAB EMP SERV CONT ASS PER INF PESQ EMP PREST SERV</t>
   </si>
   <si>
@@ -168,6 +165,9 @@
   </si>
   <si>
     <t>codigo</t>
+  </si>
+  <si>
+    <t>nomesindicato</t>
   </si>
 </sst>
 </file>
@@ -566,10 +566,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,7 +577,7 @@
         <v>19933049000125</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>356</v>
@@ -588,7 +588,7 @@
         <v>40303117000169</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>340</v>
@@ -599,7 +599,7 @@
         <v>60890928000110</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>341</v>
@@ -610,7 +610,7 @@
         <v>75992446000149</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>117</v>
@@ -621,7 +621,7 @@
         <v>76085893000187</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>346</v>
@@ -632,7 +632,7 @@
         <v>76905918000141</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>335</v>
@@ -643,7 +643,7 @@
         <v>77636363000142</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>32</v>
@@ -654,7 +654,7 @@
         <v>77841682000190</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9">
         <v>18</v>
@@ -665,7 +665,7 @@
         <v>77963841000129</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>348</v>
@@ -676,7 +676,7 @@
         <v>78105319000179</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>123</v>
@@ -687,7 +687,7 @@
         <v>78105715000104</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>345</v>
@@ -698,7 +698,7 @@
         <v>78115524000115</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>114</v>
@@ -709,7 +709,7 @@
         <v>78123999000153</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>145</v>
@@ -720,7 +720,7 @@
         <v>78472032000187</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>110</v>
@@ -731,7 +731,7 @@
         <v>78670247000102</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16">
         <v>354</v>
@@ -742,7 +742,7 @@
         <v>78675949000189</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17">
         <v>122</v>
@@ -753,7 +753,7 @@
         <v>78676665000107</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18">
         <v>130</v>
@@ -764,7 +764,7 @@
         <v>78680568000198</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19">
         <v>138</v>
@@ -775,7 +775,7 @@
         <v>78686888000155</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20">
         <v>338</v>
@@ -786,7 +786,7 @@
         <v>78686946000140</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21">
         <v>343</v>
@@ -797,7 +797,7 @@
         <v>78686953000142</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>101</v>
@@ -808,7 +808,7 @@
         <v>78687134000110</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23">
         <v>152</v>
@@ -819,7 +819,7 @@
         <v>78687431000165</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24">
         <v>347</v>
@@ -830,7 +830,7 @@
         <v>79583241000160</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25">
         <v>355</v>
@@ -841,7 +841,7 @@
         <v>79776878000173</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26">
         <v>357</v>
@@ -863,7 +863,7 @@
         <v>80869894000190</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28">
         <v>134</v>
@@ -874,7 +874,7 @@
         <v>81163164000131</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29">
         <v>124</v>
@@ -885,7 +885,7 @@
         <v>81273146000102</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -896,7 +896,7 @@
         <v>81906810000103</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31">
         <v>33</v>
@@ -904,10 +904,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
         <v>13</v>
-      </c>
-      <c r="B32" t="s">
-        <v>14</v>
       </c>
       <c r="C32">
         <v>120</v>
@@ -915,10 +915,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
         <v>30</v>
-      </c>
-      <c r="B33" t="s">
-        <v>31</v>
       </c>
       <c r="C33">
         <v>342</v>
@@ -926,10 +926,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34">
         <v>25</v>
@@ -937,10 +937,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C35">
         <v>336</v>
@@ -948,10 +948,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C36">
         <v>260</v>
